--- a/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 23:35</t>
+    <t xml:space="preserve">2026-08-17 14:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:39</t>
+    <t xml:space="preserve">2026-08-17 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 19:35</t>
+    <t xml:space="preserve">2026-09-06 20:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
